--- a/TextGame project/Assets/Resources/Story/9.xlsx
+++ b/TextGame project/Assets/Resources/Story/9.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7DDB18-C124-4A9A-9B66-B0CF7416FA7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02BA6E69-261E-4596-8C62-1E8062FDB9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -998,7 +998,7 @@
         <v>4</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>39</v>
@@ -1036,7 +1036,7 @@
         <v>4</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T4" s="1">
         <v>-640.83010000000002</v>
@@ -1059,7 +1059,7 @@
         <v>4</v>
       </c>
       <c r="S5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T5" s="1">
         <v>-640.83010000000002</v>
@@ -1082,7 +1082,7 @@
         <v>4</v>
       </c>
       <c r="S6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T6" s="1">
         <v>-640.83010000000002</v>
@@ -1105,7 +1105,7 @@
         <v>4</v>
       </c>
       <c r="S7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T7" s="1">
         <v>-640.83010000000002</v>
@@ -1128,7 +1128,7 @@
         <v>4</v>
       </c>
       <c r="S8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T8" s="1">
         <v>-640.83010000000002</v>
@@ -1151,7 +1151,7 @@
         <v>4</v>
       </c>
       <c r="S9">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T9" s="1">
         <v>-640.83010000000002</v>
@@ -1174,7 +1174,7 @@
         <v>4</v>
       </c>
       <c r="S10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T10" s="1">
         <v>-640.83010000000002</v>
@@ -1197,7 +1197,7 @@
         <v>4</v>
       </c>
       <c r="S11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T11" s="1">
         <v>-640.83010000000002</v>
@@ -1216,11 +1216,14 @@
       <c r="C12" t="s">
         <v>28</v>
       </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
       <c r="R12">
         <v>4</v>
       </c>
       <c r="S12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T12" s="1">
         <v>-640.83010000000002</v>
@@ -1243,7 +1246,7 @@
         <v>4</v>
       </c>
       <c r="S13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T13" s="1">
         <v>-640.83010000000002</v>
@@ -1266,7 +1269,7 @@
         <v>4</v>
       </c>
       <c r="S14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T14" s="1">
         <v>-640.83010000000002</v>
@@ -1289,7 +1292,7 @@
         <v>4</v>
       </c>
       <c r="S15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T15" s="1">
         <v>-640.83010000000002</v>
@@ -1312,7 +1315,7 @@
         <v>4</v>
       </c>
       <c r="S16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T16" s="1">
         <v>-640.83010000000002</v>
@@ -1335,7 +1338,7 @@
         <v>4</v>
       </c>
       <c r="S17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T17" s="1">
         <v>-640.83010000000002</v>
@@ -1358,7 +1361,7 @@
         <v>4</v>
       </c>
       <c r="S18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T18" s="1">
         <v>-640.83010000000002</v>
@@ -1381,7 +1384,7 @@
         <v>4</v>
       </c>
       <c r="S19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T19" s="1">
         <v>-640.83010000000002</v>
@@ -1404,7 +1407,7 @@
         <v>4</v>
       </c>
       <c r="S20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T20" s="1">
         <v>-640.83010000000002</v>
@@ -1427,7 +1430,7 @@
         <v>4</v>
       </c>
       <c r="S21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T21" s="1">
         <v>-640.83010000000002</v>
@@ -1450,7 +1453,7 @@
         <v>4</v>
       </c>
       <c r="S22">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T22" s="1">
         <v>-640.83010000000002</v>
@@ -1473,7 +1476,7 @@
         <v>4</v>
       </c>
       <c r="S23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T23" s="1">
         <v>-640.83010000000002</v>
@@ -1496,7 +1499,7 @@
         <v>4</v>
       </c>
       <c r="S24">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T24" s="1">
         <v>-640.83010000000002</v>
@@ -1519,7 +1522,7 @@
         <v>4</v>
       </c>
       <c r="S25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T25" s="1">
         <v>-640.83010000000002</v>
@@ -1542,7 +1545,7 @@
         <v>4</v>
       </c>
       <c r="S26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T26" s="1">
         <v>-640.83010000000002</v>
@@ -1565,7 +1568,7 @@
         <v>4</v>
       </c>
       <c r="S27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T27" s="1">
         <v>-640.83010000000002</v>
@@ -1588,7 +1591,7 @@
         <v>4</v>
       </c>
       <c r="S28">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T28" s="1">
         <v>-640.83010000000002</v>
@@ -1611,7 +1614,7 @@
         <v>4</v>
       </c>
       <c r="S29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T29" s="1">
         <v>-640.83010000000002</v>
@@ -1634,7 +1637,7 @@
         <v>4</v>
       </c>
       <c r="S30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T30" s="1">
         <v>-640.83010000000002</v>
@@ -1657,7 +1660,7 @@
         <v>4</v>
       </c>
       <c r="S31">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T31" s="1">
         <v>-640.83010000000002</v>
@@ -1680,7 +1683,7 @@
         <v>4</v>
       </c>
       <c r="S32">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T32" s="1">
         <v>-640.83010000000002</v>
@@ -1703,7 +1706,7 @@
         <v>4</v>
       </c>
       <c r="S33">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T33" s="1">
         <v>-640.83010000000002</v>
@@ -1726,7 +1729,7 @@
         <v>4</v>
       </c>
       <c r="S34">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T34" s="1">
         <v>-640.83010000000002</v>
@@ -1749,7 +1752,7 @@
         <v>4</v>
       </c>
       <c r="S35">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T35" s="1">
         <v>-640.83010000000002</v>
@@ -1772,7 +1775,7 @@
         <v>4</v>
       </c>
       <c r="S36">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T36" s="1">
         <v>-640.83010000000002</v>
@@ -1795,7 +1798,7 @@
         <v>4</v>
       </c>
       <c r="S37">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T37" s="1">
         <v>-640.83010000000002</v>
@@ -1818,7 +1821,7 @@
         <v>4</v>
       </c>
       <c r="S38">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T38" s="1">
         <v>-640.83010000000002</v>
@@ -1841,7 +1844,7 @@
         <v>4</v>
       </c>
       <c r="S39">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T39" s="1">
         <v>-640.83010000000002</v>
@@ -1864,7 +1867,7 @@
         <v>4</v>
       </c>
       <c r="S40">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T40" s="1">
         <v>-640.83010000000002</v>
@@ -1887,7 +1890,7 @@
         <v>4</v>
       </c>
       <c r="S41">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T41" s="1">
         <v>-640.83010000000002</v>
@@ -1910,7 +1913,7 @@
         <v>4</v>
       </c>
       <c r="S42">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T42" s="1">
         <v>-640.83010000000002</v>
@@ -1933,7 +1936,7 @@
         <v>4</v>
       </c>
       <c r="S43">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T43" s="1">
         <v>-640.83010000000002</v>
@@ -1956,7 +1959,7 @@
         <v>4</v>
       </c>
       <c r="S44">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T44" s="1">
         <v>-640.83010000000002</v>
@@ -1979,7 +1982,7 @@
         <v>4</v>
       </c>
       <c r="S45">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T45" s="1">
         <v>-640.83010000000002</v>
@@ -2002,7 +2005,7 @@
         <v>4</v>
       </c>
       <c r="S46">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T46" s="1">
         <v>-640.83010000000002</v>
@@ -2025,7 +2028,7 @@
         <v>4</v>
       </c>
       <c r="S47">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T47" s="1">
         <v>-640.83010000000002</v>
@@ -2048,7 +2051,7 @@
         <v>4</v>
       </c>
       <c r="S48">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T48" s="1">
         <v>-640.83010000000002</v>
@@ -2071,7 +2074,7 @@
         <v>4</v>
       </c>
       <c r="S49">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T49" s="1">
         <v>-640.83010000000002</v>
@@ -2094,7 +2097,7 @@
         <v>4</v>
       </c>
       <c r="S50">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T50" s="1">
         <v>-640.83010000000002</v>
@@ -2117,7 +2120,7 @@
         <v>4</v>
       </c>
       <c r="S51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T51" s="1">
         <v>-640.83010000000002</v>
@@ -2140,7 +2143,7 @@
         <v>4</v>
       </c>
       <c r="S52">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T52" s="1">
         <v>-640.83010000000002</v>
@@ -2163,7 +2166,7 @@
         <v>4</v>
       </c>
       <c r="S53">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T53" s="1">
         <v>-640.83010000000002</v>
@@ -2186,7 +2189,7 @@
         <v>4</v>
       </c>
       <c r="S54">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T54" s="1">
         <v>-640.83010000000002</v>
@@ -2209,7 +2212,7 @@
         <v>4</v>
       </c>
       <c r="S55">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T55" s="1">
         <v>-640.83010000000002</v>
@@ -2232,7 +2235,7 @@
         <v>4</v>
       </c>
       <c r="S56">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T56" s="1">
         <v>-640.83010000000002</v>

--- a/TextGame project/Assets/Resources/Story/9.xlsx
+++ b/TextGame project/Assets/Resources/Story/9.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02BA6E69-261E-4596-8C62-1E8062FDB9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95FE06F4-9109-4C11-89EA-D841396627EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="87">
   <si>
     <t>Name</t>
   </si>
@@ -328,6 +328,18 @@
   </si>
   <si>
     <t>（追上去）喂，你别走那么快啊！等等我！</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qianye</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qianye2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qianye1</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1009,8 +1021,8 @@
       <c r="J3" s="1">
         <v>-640.83010000000002</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>26</v>
+      <c r="K3" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>38</v>
@@ -1029,8 +1041,8 @@
       <c r="B4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C4" t="s">
-        <v>26</v>
+      <c r="C4" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="R4">
         <v>4</v>
@@ -1075,8 +1087,8 @@
       <c r="B6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C6" t="s">
-        <v>26</v>
+      <c r="C6" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="R6">
         <v>4</v>
@@ -1167,8 +1179,8 @@
       <c r="B10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C10" t="s">
-        <v>26</v>
+      <c r="C10" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="R10">
         <v>4</v>
@@ -1262,8 +1274,8 @@
       <c r="B14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C14" t="s">
-        <v>26</v>
+      <c r="C14" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="R14">
         <v>4</v>
@@ -1308,8 +1320,8 @@
       <c r="B16" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C16" t="s">
-        <v>26</v>
+      <c r="C16" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="R16">
         <v>4</v>
@@ -1354,8 +1366,8 @@
       <c r="B18" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C18" t="s">
-        <v>26</v>
+      <c r="C18" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="R18">
         <v>4</v>
@@ -1403,6 +1415,15 @@
       <c r="C20" t="s">
         <v>26</v>
       </c>
+      <c r="I20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J20" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>84</v>
+      </c>
       <c r="R20">
         <v>4</v>
       </c>
@@ -1492,8 +1513,17 @@
       <c r="B24" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C24" t="s">
-        <v>26</v>
+      <c r="C24" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J24" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="R24">
         <v>4</v>
@@ -1538,8 +1568,8 @@
       <c r="B26" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C26" t="s">
-        <v>26</v>
+      <c r="C26" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="R26">
         <v>4</v>
@@ -1584,8 +1614,8 @@
       <c r="B28" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C28" t="s">
-        <v>26</v>
+      <c r="C28" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="R28">
         <v>4</v>
@@ -1678,6 +1708,15 @@
       </c>
       <c r="C32" t="s">
         <v>26</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J32" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="R32">
         <v>4</v>
@@ -2258,7 +2297,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A56 A58:A120" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"千叶,旁白,林深"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C116" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3 C5 C7:C9 C11:C13 C15 C17 C19:C23 C25 C27 C29:C116" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Qianye,White,Linshen"</formula1>
     </dataValidation>
   </dataValidations>
